--- a/buoi_06/user_information.xlsx
+++ b/buoi_06/user_information.xlsx
@@ -451,22 +451,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4/4/2002</t>
+          <t>08/4/2002</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ducdatit2002@gmail.com</t>
+          <t>pddat@cybersoft.edu.vn</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>09204823131</t>
+          <t>0902842222</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>: giáo viên</t>
+          <t>Giảng viên</t>
         </is>
       </c>
     </row>

--- a/buoi_06/user_information.xlsx
+++ b/buoi_06/user_information.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,6 +467,87 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>Giảng viên</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Nguyễn Văn A</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>01/1/2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>vana@cybersoft.edu.vn</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>028724724724</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>GIảng viên</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>

--- a/buoi_06/user_information.xlsx
+++ b/buoi_06/user_information.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -548,6 +548,33 @@
       <c r="E5" t="inlineStr">
         <is>
           <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Phạm Văn A</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>08/02/200</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>phamducdat@cybersoft.com</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2371371734</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Giáo viên</t>
         </is>
       </c>
     </row>
